--- a/nhap-kho-2026-04-06.xlsx
+++ b/nhap-kho-2026-04-06.xlsx
@@ -1,21 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nam 4 - NTD\Ki 7\SWP\Uni-library\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8016E99A-C906-4824-9588-4403E30468CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990353F7-C98B-4B61-B347-E17C39FB7FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhap Kho" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -52,46 +47,56 @@
     <t>Mã Vị Trí *</t>
   </si>
   <si>
-    <t>69d3d6e1190253d37811055a</t>
-  </si>
-  <si>
-    <t>Refactoring</t>
-  </si>
-  <si>
-    <t>Martin Fowler</t>
-  </si>
-  <si>
-    <t>978-0134757599</t>
+    <t>69d41635d241e95b6cb2676b</t>
+  </si>
+  <si>
+    <t>Design Patterns</t>
+  </si>
+  <si>
+    <t>Gamma, Helm, Johnson, Vlissides</t>
+  </si>
+  <si>
+    <t>9780201633610</t>
   </si>
   <si>
     <t>Addison-Wesley</t>
   </si>
   <si>
-    <t>Kỹ thuật phần mềm</t>
-  </si>
-  <si>
-    <t>F2</t>
+    <t>Thiết kế phần mềm</t>
+  </si>
+  <si>
+    <t>Kệ B2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFE0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -106,14 +111,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -450,56 +457,56 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.796875" customWidth="1"/>
-    <col min="2" max="2" width="8.796875" customWidth="1"/>
-    <col min="3" max="3" width="40.796875" customWidth="1"/>
-    <col min="4" max="4" width="20.796875" customWidth="1"/>
-    <col min="5" max="5" width="16.796875" customWidth="1"/>
-    <col min="6" max="6" width="22.796875" customWidth="1"/>
-    <col min="7" max="7" width="10.796875" customWidth="1"/>
-    <col min="8" max="8" width="16.796875" customWidth="1"/>
-    <col min="9" max="9" width="20.796875" customWidth="1"/>
-    <col min="10" max="10" width="14.796875" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -519,17 +526,20 @@
       <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="I2">
-        <v>250000</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="I2" s="2">
+        <v>200000</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Lỗi" error="Vui lòng chọn mã vị trí từ danh sách thả xuống." sqref="J2" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"Kệ A1,Kệ A2,Kệ A3,Kệ A4,Kệ B1,Kệ B2,Kệ B3,Kệ B4,Kệ C1,Kệ C2,Kệ C3,Kệ C4,Kệ D1,Kệ D2,Kệ D3,Kệ D4,Kệ E1,Kệ E2,Kệ E3,Kệ E4,Kệ F1,Kệ F2,Kệ F3,Kệ F4,Kệ G1,Kệ G2,Kệ G3,Kệ G4"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:J1 A2:H2" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>